--- a/excel_template.xlsx
+++ b/excel_template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CLiCK\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4829D-0094-4993-9A0F-B7CA2390EB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AF371A-DF19-491B-A276-CE787172A117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22125" yWindow="3420" windowWidth="18180" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="설문문항_13" sheetId="1" r:id="rId1"/>
+    <sheet name="박한석" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>업무에 필요한 배경 정보와 필요 자료를 함께 제시한다</t>
   </si>
@@ -357,58 +357,6 @@
   </si>
   <si>
     <t>매우그렇다5/매우그렇지 않다1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>6, 7, 14, 15, 19, 28</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2, 10, 11, 18, 21, 25</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3, 4, 20, 22, 27, 29</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>5, 13, 26, 30</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1, 9, 17, 24</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>8, 12, 16, 23</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2, 10, 18, 25</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3, 11</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>4, 12, 19, 26</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>5, 13, 20, 27</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>6, 14, 21, 28</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>7, 15, 22, 29</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>8, 16, 23, 30</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -753,6 +701,21 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -769,21 +732,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.69921875" style="1"/>
@@ -1110,30 +1058,27 @@
     <col min="5" max="5" width="10.69921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.3984375" style="1" customWidth="1"/>
     <col min="7" max="8" width="16.5" style="1" customWidth="1"/>
-    <col min="9" max="14" width="8.69921875" style="1"/>
-    <col min="15" max="15" width="10.69921875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.3984375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.69921875" style="1"/>
+    <col min="9" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="E1" s="27" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="E1" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -1143,8 +1088,8 @@
       <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
       <c r="G3" s="9" t="s">
         <v>33</v>
       </c>
@@ -1152,7 +1097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1163,7 +1108,9 @@
         <v>5</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>37</v>
+      </c>
       <c r="G4" s="13">
         <f>SUM(C9,C10,C17,C18,C22,C31)</f>
         <v>23</v>
@@ -1172,18 +1119,8 @@
         <f>G4/6</f>
         <v>3.8333333333333335</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1194,7 +1131,9 @@
         <v>5</v>
       </c>
       <c r="E5" s="4"/>
-      <c r="F5" s="20"/>
+      <c r="F5" s="20" t="s">
+        <v>38</v>
+      </c>
       <c r="G5" s="13">
         <f>SUM(C5,C13,C14,C21,C24,C28)</f>
         <v>27</v>
@@ -1203,18 +1142,8 @@
         <f>G5/6</f>
         <v>4.5</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -1225,7 +1154,9 @@
         <v>5</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="20"/>
+      <c r="F6" s="20" t="s">
+        <v>39</v>
+      </c>
       <c r="G6" s="13">
         <f>SUM(C6,C7,C23,C25,C30,C32)</f>
         <v>19</v>
@@ -1234,18 +1165,8 @@
         <f>G6/6</f>
         <v>3.1666666666666665</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -1256,7 +1177,9 @@
         <v>5</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="20"/>
+      <c r="F7" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="G7" s="13">
         <f>SUM(C8,C16,C29,C33)</f>
         <v>15</v>
@@ -1265,18 +1188,8 @@
         <f>G7/4</f>
         <v>3.75</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1287,7 +1200,9 @@
         <v>4</v>
       </c>
       <c r="E8" s="4"/>
-      <c r="F8" s="20"/>
+      <c r="F8" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="G8" s="13">
         <f>SUM(C4,C12,C20,C27)</f>
         <v>20</v>
@@ -1296,18 +1211,8 @@
         <f>G8/4</f>
         <v>5</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -1318,7 +1223,9 @@
         <v>5</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="20"/>
+      <c r="F9" s="20" t="s">
+        <v>42</v>
+      </c>
       <c r="G9" s="13">
         <f>SUM(C11,C15,C19,C26)</f>
         <v>9</v>
@@ -1327,18 +1234,8 @@
         <f>G9/4</f>
         <v>2.25</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -1350,7 +1247,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -1360,18 +1257,16 @@
       <c r="C11" s="11">
         <v>3</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="29"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="28"/>
-      <c r="P11" s="29"/>
-    </row>
-    <row r="12" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1381,8 +1276,10 @@
       <c r="C12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="18"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="G12" s="14">
         <f>SUM(C4,C12,C20,C27)</f>
         <v>20</v>
@@ -1391,18 +1288,8 @@
         <f>G12/4</f>
         <v>5</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="21"/>
-      <c r="P12" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -1412,8 +1299,10 @@
       <c r="C13" s="11">
         <v>5</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="18"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="18" t="s">
+        <v>44</v>
+      </c>
       <c r="G13" s="14">
         <f>SUM(C5,C13,C21,C28)</f>
         <v>20</v>
@@ -1422,18 +1311,8 @@
         <f>G13/4</f>
         <v>5</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O13" s="22"/>
-      <c r="P13" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1443,8 +1322,10 @@
       <c r="C14" s="11">
         <v>3</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="18"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="18" t="s">
+        <v>45</v>
+      </c>
       <c r="G14" s="14">
         <f>C6+C14</f>
         <v>8</v>
@@ -1453,18 +1334,8 @@
         <f>G14/2</f>
         <v>4</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -1474,8 +1345,10 @@
       <c r="C15" s="11">
         <v>3</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="19"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="19" t="s">
+        <v>46</v>
+      </c>
       <c r="G15" s="15">
         <f>SUM(C7,C15,C22,C29)</f>
         <v>15</v>
@@ -1484,18 +1357,8 @@
         <f>G15/4</f>
         <v>3.75</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="24"/>
-      <c r="P15" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -1505,8 +1368,10 @@
       <c r="C16" s="11">
         <v>1</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="19"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="19" t="s">
+        <v>47</v>
+      </c>
       <c r="G16" s="15">
         <f>SUM(C8,C16,C23,C30)</f>
         <v>9</v>
@@ -1515,18 +1380,8 @@
         <f>G16/4</f>
         <v>2.25</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" s="25"/>
-      <c r="P16" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -1536,8 +1391,10 @@
       <c r="C17" s="11">
         <v>5</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="19"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="19" t="s">
+        <v>48</v>
+      </c>
       <c r="G17" s="15">
         <f>SUM(C9,C17,C24,C31)</f>
         <v>18</v>
@@ -1546,18 +1403,8 @@
         <f>G17/4</f>
         <v>4.5</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O17" s="25"/>
-      <c r="P17" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -1567,8 +1414,10 @@
       <c r="C18" s="11">
         <v>4</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="19"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="19" t="s">
+        <v>49</v>
+      </c>
       <c r="G18" s="15">
         <f>SUM(C10,C18,C25,C32)</f>
         <v>12</v>
@@ -1577,18 +1426,8 @@
         <f>G18/4</f>
         <v>3</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O18" s="25"/>
-      <c r="P18" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -1598,8 +1437,10 @@
       <c r="C19" s="11">
         <v>1</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="19"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="19" t="s">
+        <v>50</v>
+      </c>
       <c r="G19" s="15">
         <f>SUM(C11,C19,C26,C33)</f>
         <v>11</v>
@@ -1608,18 +1449,8 @@
         <f>G19/4</f>
         <v>2.75</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O19" s="26"/>
-      <c r="P19" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -1632,7 +1463,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -1645,7 +1476,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1656,7 +1487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1667,7 +1498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -1678,7 +1509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -1689,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -1700,7 +1531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -1711,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -1722,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -1733,7 +1564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -1744,7 +1575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -1755,7 +1586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -1778,16 +1609,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="O12:O14"/>
-    <mergeCell ref="O15:O19"/>
-    <mergeCell ref="E12:E14"/>
+  <mergeCells count="6">
     <mergeCell ref="E15:E19"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
